--- a/media_batches.xlsx
+++ b/media_batches.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11028"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haneenalbosta/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{24CD48CF-2F2C-0F4D-BDEF-6CBBE043DE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -70,9 +76,6 @@
     <t>MED-0001</t>
   </si>
   <si>
-    <t>Tryptone soya agar</t>
-  </si>
-  <si>
     <t>TSA-001-2026</t>
   </si>
   <si>
@@ -95,17 +98,20 @@
   </si>
   <si>
     <t>Active</t>
+  </si>
+  <si>
+    <t>TSA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,13 +176,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -214,7 +228,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -248,6 +262,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -282,9 +297,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -457,11 +473,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +515,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -507,10 +523,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
       </c>
       <c r="E2" s="2">
         <v>46026</v>
@@ -519,13 +535,13 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2">
         <v>46056</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -534,10 +550,10 @@
         <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -545,10 +561,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2">
         <v>46037</v>
@@ -557,13 +573,13 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H3" s="2">
         <v>46067</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -572,10 +588,10 @@
         <v>20</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -583,10 +599,10 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2">
         <v>46063</v>
@@ -595,13 +611,13 @@
         <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H4" s="2">
         <v>46093</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -610,10 +626,10 @@
         <v>20</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -621,10 +637,10 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2">
         <v>46071</v>
@@ -633,13 +649,13 @@
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2">
         <v>46101</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -648,10 +664,10 @@
         <v>20</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -659,10 +675,10 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3">
         <v>46093</v>
@@ -671,13 +687,13 @@
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H6" s="3">
         <v>46123</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -686,7 +702,7 @@
         <v>20</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
